--- a/data/trans_orig/P21D_6_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención fisioterapéutica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195777</t>
+          <t>195025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>282219</t>
+          <t>281247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>484306</t>
+          <t>484294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213632</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250205</t>
+          <t>250104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256352</t>
+          <t>256364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465536</t>
+          <t>465477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>471846</t>
+          <t>471874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517343</t>
+          <t>516967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314358</t>
+          <t>314723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320185</t>
+          <t>320335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>834565</t>
+          <t>835640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>845937</t>
+          <t>846041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228883</t>
+          <t>229893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216164</t>
+          <t>215819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>224058</t>
+          <t>223837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>450378</t>
+          <t>448828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460090</t>
+          <t>459633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151202</t>
+          <t>151998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177794</t>
+          <t>177553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183555</t>
+          <t>183417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332174</t>
+          <t>331571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338689</t>
+          <t>338315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115086</t>
+          <t>115396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>165379</t>
+          <t>164895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169490</t>
+          <t>169487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282564</t>
+          <t>282026</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287667</t>
+          <t>287680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19536</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>39603</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1644000</t>
+          <t>1644406</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1658617</t>
+          <t>1658234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1563628</t>
+          <t>1563533</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1579275</t>
+          <t>1579198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3214229</t>
+          <t>3215033</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3235100</t>
+          <t>3235320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_6_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_6_R-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202966</t>
+          <t>224945</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195025</t>
+          <t>217193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>248680</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281247</t>
+          <t>241969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>492426</t>
+          <t>473624</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>484294</t>
+          <t>464630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>254223</t>
+          <t>293086</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250104</t>
+          <t>288806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256364</t>
+          <t>295263</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>469709</t>
+          <t>545604</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465477</t>
+          <t>540788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>471874</t>
+          <t>547736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>523476</t>
+          <t>314079</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>516967</t>
+          <t>308809</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>316154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>318337</t>
+          <t>343306</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314723</t>
+          <t>339962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320335</t>
+          <t>345134</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>841812</t>
+          <t>657383</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>835640</t>
+          <t>651620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>846041</t>
+          <t>660632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>235161</t>
+          <t>254215</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229893</t>
+          <t>248807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>220883</t>
+          <t>247492</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215819</t>
+          <t>243041</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>223837</t>
+          <t>250890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>456044</t>
+          <t>501707</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448828</t>
+          <t>495181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459633</t>
+          <t>505636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237474</t>
+          <t>256478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>227326</t>
+          <t>254176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>510654</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>154697</t>
+          <t>172124</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151998</t>
+          <t>167387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>181167</t>
+          <t>194210</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177553</t>
+          <t>190123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183417</t>
+          <t>196756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>335864</t>
+          <t>366336</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>331571</t>
+          <t>362023</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>338315</t>
+          <t>369455</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340851</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115396</t>
+          <t>126379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>168332</t>
+          <t>184410</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164895</t>
+          <t>180873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>169487</t>
+          <t>185600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>285968</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282026</t>
+          <t>310070</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>287680</t>
+          <t>315123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17563</t>
+          <t>17198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19921</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1653372</t>
+          <t>1557637</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1644406</t>
+          <t>1549070</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1658234</t>
+          <t>1562333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1572746</t>
+          <t>1674169</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1563533</t>
+          <t>1665905</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1579198</t>
+          <t>1681041</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3226118</t>
+          <t>3231805</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3215033</t>
+          <t>3220378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3235320</t>
+          <t>3239779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1661969</t>
+          <t>1566268</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1592667</t>
+          <t>1695098</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3254636</t>
+          <t>3261365</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
